--- a/artfynd/A 45639-2024 artfynd.xlsx
+++ b/artfynd/A 45639-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121388154</v>
+        <v>121388010</v>
       </c>
       <c r="B2" t="n">
-        <v>57501</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565260</v>
+        <v>565403</v>
       </c>
       <c r="R2" t="n">
-        <v>6421829</v>
+        <v>6421954</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121388010</v>
+        <v>121388154</v>
       </c>
       <c r="B3" t="n">
-        <v>57364</v>
+        <v>57504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,29 +806,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -837,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565403</v>
+        <v>565260</v>
       </c>
       <c r="R3" t="n">
-        <v>6421954</v>
+        <v>6421829</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,11 +878,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetat torrträd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +907,7 @@
         <v>121388089</v>
       </c>
       <c r="B4" t="n">
-        <v>91092</v>
+        <v>91102</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>121388068</v>
       </c>
       <c r="B5" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 45639-2024 artfynd.xlsx
+++ b/artfynd/A 45639-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121388010</v>
+        <v>121388154</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>57504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,29 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565403</v>
+        <v>565260</v>
       </c>
       <c r="R2" t="n">
-        <v>6421954</v>
+        <v>6421829</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bearbetat torrträd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121388154</v>
+        <v>121388089</v>
       </c>
       <c r="B3" t="n">
-        <v>57504</v>
+        <v>91102</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -828,13 +827,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,7 +846,7 @@
         <v>6421829</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388089</v>
+        <v>121388068</v>
       </c>
       <c r="B4" t="n">
-        <v>91102</v>
+        <v>57367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +915,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565260</v>
+        <v>565304</v>
       </c>
       <c r="R4" t="n">
-        <v>6421829</v>
+        <v>6421840</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +995,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1018,7 +1013,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121388068</v>
+        <v>121388010</v>
       </c>
       <c r="B5" t="n">
         <v>57367</v>
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565304</v>
+        <v>565403</v>
       </c>
       <c r="R5" t="n">
-        <v>6421840</v>
+        <v>6421954</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,6 +1097,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 45639-2024 artfynd.xlsx
+++ b/artfynd/A 45639-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121388154</v>
+        <v>121388010</v>
       </c>
       <c r="B2" t="n">
-        <v>57504</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565260</v>
+        <v>565403</v>
       </c>
       <c r="R2" t="n">
-        <v>6421829</v>
+        <v>6421954</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121388089</v>
+        <v>121388154</v>
       </c>
       <c r="B3" t="n">
-        <v>91102</v>
+        <v>57504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,12 +828,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -846,7 +848,7 @@
         <v>6421829</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +886,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388068</v>
+        <v>121388089</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>91114</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,35 +916,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565304</v>
+        <v>565260</v>
       </c>
       <c r="R4" t="n">
-        <v>6421840</v>
+        <v>6421829</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,6 +999,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1013,7 +1018,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121388010</v>
+        <v>121388068</v>
       </c>
       <c r="B5" t="n">
         <v>57367</v>
@@ -1061,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565403</v>
+        <v>565304</v>
       </c>
       <c r="R5" t="n">
-        <v>6421954</v>
+        <v>6421840</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,11 +1102,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bearbetat torrträd</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 45639-2024 artfynd.xlsx
+++ b/artfynd/A 45639-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121388010</v>
+        <v>121388089</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>91115</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565403</v>
+        <v>565260</v>
       </c>
       <c r="R2" t="n">
-        <v>6421954</v>
+        <v>6421829</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,17 +764,13 @@
           <t>2024-11-28</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bearbetat torrträd</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121388154</v>
+        <v>121388068</v>
       </c>
       <c r="B3" t="n">
-        <v>57504</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,33 +805,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -842,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565260</v>
+        <v>565304</v>
       </c>
       <c r="R3" t="n">
-        <v>6421829</v>
+        <v>6421840</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388089</v>
+        <v>121388010</v>
       </c>
       <c r="B4" t="n">
-        <v>91114</v>
+        <v>57367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +911,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565260</v>
+        <v>565403</v>
       </c>
       <c r="R4" t="n">
-        <v>6421829</v>
+        <v>6421954</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,13 +985,17 @@
           <t>2024-11-28</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1018,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121388068</v>
+        <v>121388154</v>
       </c>
       <c r="B5" t="n">
-        <v>57367</v>
+        <v>57504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,29 +1030,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565304</v>
+        <v>565260</v>
       </c>
       <c r="R5" t="n">
-        <v>6421840</v>
+        <v>6421829</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 45639-2024 artfynd.xlsx
+++ b/artfynd/A 45639-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121388089</v>
+        <v>121388010</v>
       </c>
       <c r="B2" t="n">
-        <v>91115</v>
+        <v>57370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565260</v>
+        <v>565403</v>
       </c>
       <c r="R2" t="n">
-        <v>6421829</v>
+        <v>6421954</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,13 +761,17 @@
           <t>2024-11-28</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121388068</v>
+        <v>121388089</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>91118</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,35 +802,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565304</v>
+        <v>565260</v>
       </c>
       <c r="R3" t="n">
-        <v>6421840</v>
+        <v>6421829</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,6 +885,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388010</v>
+        <v>121388154</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,29 +920,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -947,13 +956,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565403</v>
+        <v>565260</v>
       </c>
       <c r="R4" t="n">
-        <v>6421954</v>
+        <v>6421829</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,11 +992,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bearbetat torrträd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121388154</v>
+        <v>121388068</v>
       </c>
       <c r="B5" t="n">
-        <v>57504</v>
+        <v>57370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,33 +1034,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565260</v>
+        <v>565304</v>
       </c>
       <c r="R5" t="n">
-        <v>6421829</v>
+        <v>6421840</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 45639-2024 artfynd.xlsx
+++ b/artfynd/A 45639-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121388010</v>
+        <v>121388089</v>
       </c>
       <c r="B2" t="n">
-        <v>57370</v>
+        <v>91118</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565403</v>
+        <v>565260</v>
       </c>
       <c r="R2" t="n">
-        <v>6421954</v>
+        <v>6421829</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,17 +764,13 @@
           <t>2024-11-28</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bearbetat torrträd</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121388089</v>
+        <v>121388154</v>
       </c>
       <c r="B3" t="n">
-        <v>91118</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -828,12 +827,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>6421829</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388154</v>
+        <v>121388010</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>57370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,33 +919,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -956,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565260</v>
+        <v>565403</v>
       </c>
       <c r="R4" t="n">
-        <v>6421829</v>
+        <v>6421954</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,6 +987,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 45639-2024 artfynd.xlsx
+++ b/artfynd/A 45639-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121388089</v>
+        <v>121388010</v>
       </c>
       <c r="B2" t="n">
-        <v>91118</v>
+        <v>57371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565260</v>
+        <v>565403</v>
       </c>
       <c r="R2" t="n">
-        <v>6421829</v>
+        <v>6421954</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,13 +761,17 @@
           <t>2024-11-28</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121388154</v>
+        <v>121388068</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>57371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,33 +806,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -841,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565260</v>
+        <v>565304</v>
       </c>
       <c r="R3" t="n">
-        <v>6421829</v>
+        <v>6421840</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -903,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388010</v>
+        <v>121388089</v>
       </c>
       <c r="B4" t="n">
-        <v>57370</v>
+        <v>91124</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,35 +912,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565403</v>
+        <v>565260</v>
       </c>
       <c r="R4" t="n">
-        <v>6421954</v>
+        <v>6421829</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,17 +989,13 @@
           <t>2024-11-28</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bearbetat torrträd</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1018,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121388068</v>
+        <v>121388154</v>
       </c>
       <c r="B5" t="n">
-        <v>57370</v>
+        <v>57508</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,29 +1030,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565304</v>
+        <v>565260</v>
       </c>
       <c r="R5" t="n">
-        <v>6421840</v>
+        <v>6421829</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 45639-2024 artfynd.xlsx
+++ b/artfynd/A 45639-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121388010</v>
       </c>
       <c r="B2" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>121388068</v>
       </c>
       <c r="B3" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>121388089</v>
       </c>
       <c r="B4" t="n">
-        <v>91124</v>
+        <v>91125</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>121388154</v>
       </c>
       <c r="B5" t="n">
-        <v>57508</v>
+        <v>57509</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 45639-2024 artfynd.xlsx
+++ b/artfynd/A 45639-2024 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121388068</v>
+        <v>121388089</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>91125</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,35 +802,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565304</v>
+        <v>565260</v>
       </c>
       <c r="R3" t="n">
-        <v>6421840</v>
+        <v>6421829</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,6 +885,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388089</v>
+        <v>121388154</v>
       </c>
       <c r="B4" t="n">
-        <v>91125</v>
+        <v>57509</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,25 +916,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -938,12 +942,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,7 +962,7 @@
         <v>6421829</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,7 +1000,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1014,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121388154</v>
+        <v>121388068</v>
       </c>
       <c r="B5" t="n">
-        <v>57509</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,33 +1034,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565260</v>
+        <v>565304</v>
       </c>
       <c r="R5" t="n">
-        <v>6421829</v>
+        <v>6421840</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 45639-2024 artfynd.xlsx
+++ b/artfynd/A 45639-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121388010</v>
+        <v>121388068</v>
       </c>
       <c r="B2" t="n">
         <v>57372</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565403</v>
+        <v>565304</v>
       </c>
       <c r="R2" t="n">
-        <v>6421954</v>
+        <v>6421840</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,11 +759,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bearbetat torrträd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1018,7 +1013,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121388068</v>
+        <v>121388010</v>
       </c>
       <c r="B5" t="n">
         <v>57372</v>
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565304</v>
+        <v>565403</v>
       </c>
       <c r="R5" t="n">
-        <v>6421840</v>
+        <v>6421954</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,6 +1097,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 45639-2024 artfynd.xlsx
+++ b/artfynd/A 45639-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121388068</v>
+        <v>121388010</v>
       </c>
       <c r="B2" t="n">
         <v>57372</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565304</v>
+        <v>565403</v>
       </c>
       <c r="R2" t="n">
-        <v>6421840</v>
+        <v>6421954</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121388089</v>
+        <v>121388154</v>
       </c>
       <c r="B3" t="n">
-        <v>91125</v>
+        <v>57509</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -823,12 +828,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,7 +848,7 @@
         <v>6421829</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +886,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388154</v>
+        <v>121388089</v>
       </c>
       <c r="B4" t="n">
-        <v>57509</v>
+        <v>91125</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +916,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,13 +942,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,7 +961,7 @@
         <v>6421829</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,6 +999,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1013,7 +1018,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121388010</v>
+        <v>121388068</v>
       </c>
       <c r="B5" t="n">
         <v>57372</v>
@@ -1061,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565403</v>
+        <v>565304</v>
       </c>
       <c r="R5" t="n">
-        <v>6421954</v>
+        <v>6421840</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,11 +1102,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bearbetat torrträd</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 45639-2024 artfynd.xlsx
+++ b/artfynd/A 45639-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121388010</v>
+        <v>121388068</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565403</v>
+        <v>565304</v>
       </c>
       <c r="R2" t="n">
-        <v>6421954</v>
+        <v>6421840</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,11 +759,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bearbetat torrträd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121388154</v>
+        <v>121388089</v>
       </c>
       <c r="B3" t="n">
-        <v>57509</v>
+        <v>91133</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -828,13 +823,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,7 +842,7 @@
         <v>6421829</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,6 +880,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388089</v>
+        <v>121388010</v>
       </c>
       <c r="B4" t="n">
-        <v>91125</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +911,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565260</v>
+        <v>565403</v>
       </c>
       <c r="R4" t="n">
-        <v>6421829</v>
+        <v>6421954</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,13 +985,17 @@
           <t>2024-11-28</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1018,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121388068</v>
+        <v>121388154</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
+        <v>57510</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,29 +1030,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565304</v>
+        <v>565260</v>
       </c>
       <c r="R5" t="n">
-        <v>6421840</v>
+        <v>6421829</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
